--- a/pipeline_output/RJ_2W_H&M.xlsx
+++ b/pipeline_output/RJ_2W_H&M.xlsx
@@ -736,12 +736,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1605,12 +1605,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8233,12 +8233,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -8945,12 +8945,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9189,12 +9189,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9306,12 +9306,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9433,12 +9433,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10399,12 +10399,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10526,12 +10526,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10770,12 +10770,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -11004,12 +11004,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -11121,12 +11121,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -11609,12 +11609,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -11863,12 +11863,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -11980,12 +11980,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -12214,12 +12214,12 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -12468,12 +12468,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -12595,12 +12595,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -12722,12 +12722,12 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -12839,12 +12839,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -12956,12 +12956,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -13190,12 +13190,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -13307,12 +13307,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -13434,12 +13434,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -13688,12 +13688,12 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -13815,12 +13815,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -13932,12 +13932,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -14186,12 +14186,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -14303,12 +14303,12 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -14430,12 +14430,12 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -14557,12 +14557,12 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -14674,12 +14674,12 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -14801,12 +14801,12 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -14928,12 +14928,12 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -15045,12 +15045,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -15172,12 +15172,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -15299,12 +15299,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -15426,12 +15426,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -15553,12 +15553,12 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -15670,12 +15670,12 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -15904,12 +15904,12 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -16021,12 +16021,12 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -16138,12 +16138,12 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -16265,12 +16265,12 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -16392,12 +16392,12 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -16646,12 +16646,12 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -16763,12 +16763,12 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -16890,12 +16890,12 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -17017,12 +17017,12 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -17134,12 +17134,12 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -17261,12 +17261,12 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -17388,12 +17388,12 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -17505,12 +17505,12 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -17632,12 +17632,12 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -17759,12 +17759,12 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -17876,12 +17876,12 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -18003,12 +18003,12 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -18130,12 +18130,12 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -18257,12 +18257,12 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -18384,12 +18384,12 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -18501,12 +18501,12 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -18618,12 +18618,12 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -18735,12 +18735,12 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -18755,7 +18755,7 @@
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>750</t>
         </is>
       </c>
     </row>
@@ -18852,12 +18852,12 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -18969,12 +18969,12 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -19096,12 +19096,12 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -19223,12 +19223,12 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -19350,12 +19350,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -19594,12 +19594,12 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -19721,12 +19721,12 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -19848,12 +19848,12 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -19965,12 +19965,12 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -20092,12 +20092,12 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -20219,12 +20219,12 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -20336,12 +20336,12 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -20590,12 +20590,12 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -20717,12 +20717,12 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -20971,12 +20971,12 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -21098,12 +21098,12 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -21225,12 +21225,12 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -21352,12 +21352,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -21479,12 +21479,12 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -21606,12 +21606,12 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -21723,12 +21723,12 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -21840,12 +21840,12 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -21957,12 +21957,12 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -22074,12 +22074,12 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -22191,12 +22191,12 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -22308,12 +22308,12 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -22425,12 +22425,12 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -22542,12 +22542,12 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -22659,12 +22659,12 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -22776,12 +22776,12 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -22893,12 +22893,12 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -23010,12 +23010,12 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -23127,12 +23127,12 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -23244,12 +23244,12 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -23361,12 +23361,12 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
@@ -23478,12 +23478,12 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
